--- a/artfynd/A 60996-2021 artfynd.xlsx
+++ b/artfynd/A 60996-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60996-2021 artfynd.xlsx
+++ b/artfynd/A 60996-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6223682</v>
+        <v>93337696</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stuverum, 240 m NNO-ut, Ög</t>
+          <t>Stuverum, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563503.3654230972</v>
+        <v>563518</v>
       </c>
       <c r="R2" t="n">
-        <v>6415993.627047304</v>
+        <v>6415965</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-10-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-10-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,86 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>fuktig granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>David Ek, Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92005648</v>
+        <v>93337728</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stuverum, Jössebäck, Ög</t>
+          <t>Stuverum, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563474.5122262404</v>
+        <v>563604</v>
       </c>
       <c r="R3" t="n">
-        <v>6416066.029528228</v>
+        <v>6416002</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2021-05-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,65 +857,71 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>David Ek</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>David Ek, Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93337728</v>
+        <v>92004966</v>
       </c>
       <c r="B4" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stuverum, Ög</t>
+          <t>Stuverum, Jössebäck, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563603.9282826377</v>
+        <v>563845</v>
       </c>
       <c r="R4" t="n">
-        <v>6416002.665825623</v>
+        <v>6415760</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +945,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,33 +969,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Ek, Magnus Wadstein</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>93337696</v>
+        <v>92005648</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,37 +999,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stuverum, Ög</t>
+          <t>Stuverum, Jössebäck, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563518.7273227046</v>
+        <v>563475</v>
       </c>
       <c r="R5" t="n">
-        <v>6415965.683522575</v>
+        <v>6416066</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1065,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,27 +1095,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Ek</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Ek, Magnus Wadstein</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97102392</v>
+        <v>97102186</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1137,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1179,23 +1145,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
+          <t>A60996, Stuverum, Odensvi, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563828.9752119737</v>
+        <v>563847</v>
       </c>
       <c r="R6" t="n">
-        <v>6415823.289046627</v>
+        <v>6415832</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,19 +1187,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,54 +1205,49 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Mariann Gustafsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97102394</v>
+        <v>97102192</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1308,23 +1255,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
+          <t>A60996, Stuverum, Odensvi, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563828.9752119737</v>
+        <v>563846</v>
       </c>
       <c r="R7" t="n">
-        <v>6415823.289046627</v>
+        <v>6415828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,19 +1297,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,54 +1315,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Mariann Gustafsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97102412</v>
+        <v>97102214</v>
       </c>
       <c r="B8" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1437,23 +1365,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
+          <t>A60996, Stuverum, Odensvi, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563815.2004587637</v>
+        <v>563856</v>
       </c>
       <c r="R8" t="n">
-        <v>6415818.283268846</v>
+        <v>6415809</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1483,19 +1407,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,27 +1425,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Mariann Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97102186</v>
+        <v>97102225</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563846.960959937</v>
+        <v>563860</v>
       </c>
       <c r="R9" t="n">
-        <v>6415831.552965692</v>
+        <v>6415796</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,19 +1517,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>97102402</v>
+        <v>97102392</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1683,7 +1577,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1704,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563815.2004587637</v>
+        <v>563829</v>
       </c>
       <c r="R10" t="n">
-        <v>6415818.283268846</v>
+        <v>6415823</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,19 +1631,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,15 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>97102192</v>
+        <v>97102402</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1691,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1820,19 +1699,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A60996, Stuverum, Odensvi, Ög</t>
+          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563845.9462841206</v>
+        <v>563815</v>
       </c>
       <c r="R11" t="n">
-        <v>6415828.345735836</v>
+        <v>6415818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,19 +1745,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,12 +1763,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Stefan Kasselstrand, Mariann Gustafsson</t>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1905,12 +1778,7 @@
         <v>97103005</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,10 +1826,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563741.007816175</v>
+        <v>563741</v>
       </c>
       <c r="R12" t="n">
-        <v>6415826.14513572</v>
+        <v>6415826</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1991,19 +1859,9 @@
           <t>2021-11-11</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-11-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2036,15 +1894,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113161245</v>
+        <v>97102394</v>
       </c>
       <c r="B13" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,37 +1905,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stuverum, Ög</t>
+          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563809</v>
+        <v>563829</v>
       </c>
       <c r="R13" t="n">
-        <v>6415863</v>
+        <v>6415823</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2106,12 +1975,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2021-11-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2120,21 +1989,430 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>97102412</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stuverum Avverkningsanmälan A60996, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563815</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6415818</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-11-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113161245</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stuverum, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563809</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6415863</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Jonas Örnborg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>6223682</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stuverum, 240 m NNO-ut, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>563503</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415994</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2011-10-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>86038072</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stuverum, 335 m O, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>563771</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6415769</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-06-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>torräng i skogsbilvägkant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Svenson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
